--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ17"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,32 +680,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129000932</v>
+        <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>79327</v>
+        <v>92065</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -715,17 +715,17 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Kainulasjärvi, Nb</t>
+          <t>Narken, Nb</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>835803</v>
+        <v>835924</v>
       </c>
       <c r="R2" t="n">
-        <v>7457228</v>
+        <v>7457004</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -749,12 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -785,13 +795,13 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000932</t>
+          <t>https://artportalen.se/Sighting/136193841</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000945</v>
+        <v>129000932</v>
       </c>
       <c r="B3" t="n">
         <v>79327</v>
@@ -830,10 +840,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>835499</v>
+        <v>835803</v>
       </c>
       <c r="R3" t="n">
-        <v>7457107</v>
+        <v>7457228</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -896,13 +906,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000945</t>
+          <t>https://artportalen.se/Sighting/129000932</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000957</v>
+        <v>129000945</v>
       </c>
       <c r="B4" t="n">
         <v>79327</v>
@@ -937,14 +947,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Narken, Nb</t>
+          <t>Kainulasjärvi, Nb</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>835930</v>
+        <v>835499</v>
       </c>
       <c r="R4" t="n">
-        <v>7457049</v>
+        <v>7457107</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1007,38 +1017,38 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000957</t>
+          <t>https://artportalen.se/Sighting/129000945</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000959</v>
+        <v>129000957</v>
       </c>
       <c r="B5" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1052,10 +1062,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>835944</v>
+        <v>835930</v>
       </c>
       <c r="R5" t="n">
-        <v>7457045</v>
+        <v>7457049</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1118,16 +1128,16 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000959</t>
+          <t>https://artportalen.se/Sighting/129000957</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000954</v>
+        <v>129000959</v>
       </c>
       <c r="B6" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1135,21 +1145,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1163,10 +1173,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>835857</v>
+        <v>835944</v>
       </c>
       <c r="R6" t="n">
-        <v>7457081</v>
+        <v>7457045</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1229,38 +1239,38 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000954</t>
+          <t>https://artportalen.se/Sighting/129000959</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000946</v>
+        <v>129000954</v>
       </c>
       <c r="B7" t="n">
-        <v>80461</v>
+        <v>79084</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1270,14 +1280,14 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kainulasjärvi, Nb</t>
+          <t>Narken, Nb</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>835526</v>
+        <v>835857</v>
       </c>
       <c r="R7" t="n">
-        <v>7457087</v>
+        <v>7457081</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1340,13 +1350,13 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000946</t>
+          <t>https://artportalen.se/Sighting/129000954</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000952</v>
+        <v>129000946</v>
       </c>
       <c r="B8" t="n">
         <v>80461</v>
@@ -1381,14 +1391,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Narken, Nb</t>
+          <t>Kainulasjärvi, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>835878</v>
+        <v>835526</v>
       </c>
       <c r="R8" t="n">
-        <v>7457112</v>
+        <v>7457087</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1451,13 +1461,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000952</t>
+          <t>https://artportalen.se/Sighting/129000946</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000955</v>
+        <v>129000952</v>
       </c>
       <c r="B9" t="n">
         <v>80461</v>
@@ -1496,10 +1506,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>835909</v>
+        <v>835878</v>
       </c>
       <c r="R9" t="n">
-        <v>7457069</v>
+        <v>7457112</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1562,13 +1572,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000955</t>
+          <t>https://artportalen.se/Sighting/129000952</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129000960</v>
+        <v>129000955</v>
       </c>
       <c r="B10" t="n">
         <v>80461</v>
@@ -1607,10 +1617,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>835953</v>
+        <v>835909</v>
       </c>
       <c r="R10" t="n">
-        <v>7457039</v>
+        <v>7457069</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1673,16 +1683,16 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000960</t>
+          <t>https://artportalen.se/Sighting/129000955</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000951</v>
+        <v>129000960</v>
       </c>
       <c r="B11" t="n">
-        <v>58327</v>
+        <v>80461</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1690,26 +1700,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1718,10 +1728,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>835875</v>
+        <v>835953</v>
       </c>
       <c r="R11" t="n">
-        <v>7457126</v>
+        <v>7457039</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1784,55 +1794,55 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000951</t>
+          <t>https://artportalen.se/Sighting/129000960</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129000934</v>
+        <v>129000951</v>
       </c>
       <c r="B12" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Kainulasjärvi, Nb</t>
+          <t>Narken, Nb</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>835773</v>
+        <v>835875</v>
       </c>
       <c r="R12" t="n">
-        <v>7457205</v>
+        <v>7457126</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1895,43 +1905,43 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000934</t>
+          <t>https://artportalen.se/Sighting/129000951</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129000935</v>
+        <v>129000934</v>
       </c>
       <c r="B13" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1940,10 +1950,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>835717</v>
+        <v>835773</v>
       </c>
       <c r="R13" t="n">
-        <v>7457203</v>
+        <v>7457205</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2006,13 +2016,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000935</t>
+          <t>https://artportalen.se/Sighting/129000934</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129000940</v>
+        <v>129000935</v>
       </c>
       <c r="B14" t="n">
         <v>99118</v>
@@ -2051,10 +2061,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835693</v>
+        <v>835717</v>
       </c>
       <c r="R14" t="n">
-        <v>7457091</v>
+        <v>7457203</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2117,13 +2127,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000940</t>
+          <t>https://artportalen.se/Sighting/129000935</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129000942</v>
+        <v>129000940</v>
       </c>
       <c r="B15" t="n">
         <v>99118</v>
@@ -2162,10 +2172,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835683</v>
+        <v>835693</v>
       </c>
       <c r="R15" t="n">
-        <v>7457074</v>
+        <v>7457091</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2228,43 +2238,43 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000942</t>
+          <t>https://artportalen.se/Sighting/129000940</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129000939</v>
+        <v>129000942</v>
       </c>
       <c r="B16" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
@@ -2273,10 +2283,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835720</v>
+        <v>835683</v>
       </c>
       <c r="R16" t="n">
-        <v>7457126</v>
+        <v>7457074</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2339,13 +2349,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000939</t>
+          <t>https://artportalen.se/Sighting/129000942</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129000949</v>
+        <v>129000939</v>
       </c>
       <c r="B17" t="n">
         <v>97989</v>
@@ -2375,7 +2385,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2384,10 +2394,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835780</v>
+        <v>835720</v>
       </c>
       <c r="R17" t="n">
-        <v>7457116</v>
+        <v>7457126</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2449,6 +2459,117 @@
       </c>
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000939</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>129000949</v>
+      </c>
+      <c r="B18" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Kainulasjärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>835780</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7457116</v>
+      </c>
+      <c r="S18" t="n">
+        <v>1</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129000949</t>
         </is>
@@ -2472,6 +2593,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92065</v>
+        <v>92066</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92066</v>
+        <v>92067</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92067</v>
+        <v>92073</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92073</v>
+        <v>92074</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92074</v>
+        <v>92080</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92080</v>
+        <v>92087</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92087</v>
+        <v>92088</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92088</v>
+        <v>92101</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ18"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -801,32 +801,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129000932</v>
+        <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>79327</v>
+        <v>92497</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>4217</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blodticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Meruliopsis taxicola</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Pers.:Fr.) Bondartsev</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -836,14 +836,14 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Kainulasjärvi, Nb</t>
+          <t>Narken, Nb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>835803</v>
+        <v>835923</v>
       </c>
       <c r="R3" t="n">
-        <v>7457228</v>
+        <v>7457006</v>
       </c>
       <c r="S3" t="n">
         <v>1</v>
@@ -870,12 +870,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-08-25</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -906,13 +916,13 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000932</t>
+          <t>https://artportalen.se/Sighting/136481036</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129000945</v>
+        <v>129000932</v>
       </c>
       <c r="B4" t="n">
         <v>79327</v>
@@ -951,10 +961,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>835499</v>
+        <v>835803</v>
       </c>
       <c r="R4" t="n">
-        <v>7457107</v>
+        <v>7457228</v>
       </c>
       <c r="S4" t="n">
         <v>1</v>
@@ -1017,13 +1027,13 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000945</t>
+          <t>https://artportalen.se/Sighting/129000932</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>129000957</v>
+        <v>129000945</v>
       </c>
       <c r="B5" t="n">
         <v>79327</v>
@@ -1058,14 +1068,14 @@
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Narken, Nb</t>
+          <t>Kainulasjärvi, Nb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>835930</v>
+        <v>835499</v>
       </c>
       <c r="R5" t="n">
-        <v>7457049</v>
+        <v>7457107</v>
       </c>
       <c r="S5" t="n">
         <v>1</v>
@@ -1128,38 +1138,38 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000957</t>
+          <t>https://artportalen.se/Sighting/129000945</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>129000959</v>
+        <v>129000957</v>
       </c>
       <c r="B6" t="n">
-        <v>83307</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6440</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1173,10 +1183,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>835944</v>
+        <v>835930</v>
       </c>
       <c r="R6" t="n">
-        <v>7457045</v>
+        <v>7457049</v>
       </c>
       <c r="S6" t="n">
         <v>1</v>
@@ -1239,16 +1249,16 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000959</t>
+          <t>https://artportalen.se/Sighting/129000957</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>129000954</v>
+        <v>129000959</v>
       </c>
       <c r="B7" t="n">
-        <v>79084</v>
+        <v>83307</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1256,21 +1266,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6446</v>
+        <v>6440</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1284,10 +1294,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>835857</v>
+        <v>835944</v>
       </c>
       <c r="R7" t="n">
-        <v>7457081</v>
+        <v>7457045</v>
       </c>
       <c r="S7" t="n">
         <v>1</v>
@@ -1350,38 +1360,38 @@
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000954</t>
+          <t>https://artportalen.se/Sighting/129000959</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>129000946</v>
+        <v>129000954</v>
       </c>
       <c r="B8" t="n">
-        <v>80461</v>
+        <v>79084</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6462</v>
+        <v>6446</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -1391,14 +1401,14 @@
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Kainulasjärvi, Nb</t>
+          <t>Narken, Nb</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>835526</v>
+        <v>835857</v>
       </c>
       <c r="R8" t="n">
-        <v>7457087</v>
+        <v>7457081</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
@@ -1461,13 +1471,13 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000946</t>
+          <t>https://artportalen.se/Sighting/129000954</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>129000952</v>
+        <v>129000946</v>
       </c>
       <c r="B9" t="n">
         <v>80461</v>
@@ -1502,14 +1512,14 @@
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Narken, Nb</t>
+          <t>Kainulasjärvi, Nb</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>835878</v>
+        <v>835526</v>
       </c>
       <c r="R9" t="n">
-        <v>7457112</v>
+        <v>7457087</v>
       </c>
       <c r="S9" t="n">
         <v>1</v>
@@ -1572,13 +1582,13 @@
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000952</t>
+          <t>https://artportalen.se/Sighting/129000946</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>129000955</v>
+        <v>129000952</v>
       </c>
       <c r="B10" t="n">
         <v>80461</v>
@@ -1617,10 +1627,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>835909</v>
+        <v>835878</v>
       </c>
       <c r="R10" t="n">
-        <v>7457069</v>
+        <v>7457112</v>
       </c>
       <c r="S10" t="n">
         <v>1</v>
@@ -1683,13 +1693,13 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000955</t>
+          <t>https://artportalen.se/Sighting/129000952</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>129000960</v>
+        <v>129000955</v>
       </c>
       <c r="B11" t="n">
         <v>80461</v>
@@ -1728,10 +1738,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>835953</v>
+        <v>835909</v>
       </c>
       <c r="R11" t="n">
-        <v>7457039</v>
+        <v>7457069</v>
       </c>
       <c r="S11" t="n">
         <v>1</v>
@@ -1794,16 +1804,16 @@
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000960</t>
+          <t>https://artportalen.se/Sighting/129000955</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>129000951</v>
+        <v>129000960</v>
       </c>
       <c r="B12" t="n">
-        <v>58327</v>
+        <v>80461</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,26 +1821,26 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103015</v>
+        <v>6462</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
@@ -1839,10 +1849,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>835875</v>
+        <v>835953</v>
       </c>
       <c r="R12" t="n">
-        <v>7457126</v>
+        <v>7457039</v>
       </c>
       <c r="S12" t="n">
         <v>1</v>
@@ -1905,55 +1915,55 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000951</t>
+          <t>https://artportalen.se/Sighting/129000960</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>129000934</v>
+        <v>129000951</v>
       </c>
       <c r="B13" t="n">
-        <v>58114</v>
+        <v>58327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103021</v>
+        <v>103015</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Kainulasjärvi, Nb</t>
+          <t>Narken, Nb</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>835773</v>
+        <v>835875</v>
       </c>
       <c r="R13" t="n">
-        <v>7457205</v>
+        <v>7457126</v>
       </c>
       <c r="S13" t="n">
         <v>1</v>
@@ -2016,43 +2026,43 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000934</t>
+          <t>https://artportalen.se/Sighting/129000951</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>129000935</v>
+        <v>129000934</v>
       </c>
       <c r="B14" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -2061,10 +2071,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>835717</v>
+        <v>835773</v>
       </c>
       <c r="R14" t="n">
-        <v>7457203</v>
+        <v>7457205</v>
       </c>
       <c r="S14" t="n">
         <v>1</v>
@@ -2127,13 +2137,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000935</t>
+          <t>https://artportalen.se/Sighting/129000934</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>129000940</v>
+        <v>129000935</v>
       </c>
       <c r="B15" t="n">
         <v>99118</v>
@@ -2172,10 +2182,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>835693</v>
+        <v>835717</v>
       </c>
       <c r="R15" t="n">
-        <v>7457091</v>
+        <v>7457203</v>
       </c>
       <c r="S15" t="n">
         <v>1</v>
@@ -2238,13 +2248,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000940</t>
+          <t>https://artportalen.se/Sighting/129000935</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>129000942</v>
+        <v>129000940</v>
       </c>
       <c r="B16" t="n">
         <v>99118</v>
@@ -2283,10 +2293,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>835683</v>
+        <v>835693</v>
       </c>
       <c r="R16" t="n">
-        <v>7457074</v>
+        <v>7457091</v>
       </c>
       <c r="S16" t="n">
         <v>1</v>
@@ -2349,43 +2359,43 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000942</t>
+          <t>https://artportalen.se/Sighting/129000940</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>129000939</v>
+        <v>129000942</v>
       </c>
       <c r="B17" t="n">
-        <v>97989</v>
+        <v>99118</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>221941</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
@@ -2394,10 +2404,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>835720</v>
+        <v>835683</v>
       </c>
       <c r="R17" t="n">
-        <v>7457126</v>
+        <v>7457074</v>
       </c>
       <c r="S17" t="n">
         <v>1</v>
@@ -2460,13 +2470,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129000939</t>
+          <t>https://artportalen.se/Sighting/129000942</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>129000949</v>
+        <v>129000939</v>
       </c>
       <c r="B18" t="n">
         <v>97989</v>
@@ -2496,7 +2506,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
@@ -2505,10 +2515,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>835780</v>
+        <v>835720</v>
       </c>
       <c r="R18" t="n">
-        <v>7457116</v>
+        <v>7457126</v>
       </c>
       <c r="S18" t="n">
         <v>1</v>
@@ -2570,6 +2580,117 @@
       </c>
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129000939</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>129000949</v>
+      </c>
+      <c r="B19" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Kainulasjärvi, Nb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>835780</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7457116</v>
+      </c>
+      <c r="S19" t="n">
+        <v>1</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Pajala</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Tärendö</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-09-18</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Påträffad under Sveaskogs naturvärdesinventering</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Mimmi Persson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/129000949</t>
         </is>
@@ -2594,6 +2715,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 35239-2026 artfynd.xlsx
+++ b/artfynd/A 35239-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193841</v>
       </c>
       <c r="B2" t="n">
-        <v>92101</v>
+        <v>92102</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136481036</v>
       </c>
       <c r="B3" t="n">
-        <v>92497</v>
+        <v>92498</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
